--- a/assets/data/excel/chipSkills.xlsx
+++ b/assets/data/excel/chipSkills.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="芯片技能表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chipSkills" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,22 +444,37 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>triggerCondition</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>effectType</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>effectValue</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>targetScope</t>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>maxStack</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>cooldown</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>weight</t>
         </is>
       </c>
     </row>
@@ -501,12 +516,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>string</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>int</t>
         </is>
       </c>
     </row>
@@ -518,42 +548,57 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>技能名称</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>英文名</t>
+          <t>英文名称</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>类型</t>
+          <t>技能类型(aura/trigger/modify)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>技能描述</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>触发条件(仅trigger类型)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>效果类型</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>效果值</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>效果数值</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>持续回合</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>目标范围</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>最大叠加层数</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>冷却回合</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>权重</t>
         </is>
       </c>
     </row>
@@ -565,12 +610,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>坚韧</t>
+          <t>锈蚀增幅</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Rust Amplifier</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -580,26 +625,29 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>提升佩戴者3%减伤率</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>damage_reduction</t>
-        </is>
-      </c>
+          <t>常驻光环：佩戴者攻击力提升3%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>buffAtk</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.03</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -610,41 +658,48 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>锋利</t>
+          <t>过载脉冲</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sharpness</t>
+          <t>Overload Pulse</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>aura</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>提升佩戴者3%攻击力</t>
+          <t>攻击时触发：对目标造成攻击力8%的真实伤害</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>atk_boost</t>
+          <t>onAttack</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>trueDamage</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.08</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="6">
@@ -655,41 +710,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>均衡</t>
+          <t>热能导引</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>Thermal Guidance</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>aura</t>
+          <t>modify</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>提升佩戴者1%攻击力和2%生命值</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>atk_hp_boost</t>
-        </is>
-      </c>
+          <t>永久提升佩戴者暴击率5%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.01,0.02</t>
+          <t>buffCrit</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.05</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>110</v>
       </c>
     </row>
     <row r="7">
@@ -700,41 +758,48 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>守护光环</t>
+          <t>裂变弹头</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Guardian Aura</t>
+          <t>Fission Warhead</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>aura</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>佩戴者生命值+5%，周围友军减伤3%</t>
+          <t>攻击时触发：额外造成攻击力12%的真实伤害</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>team_damage_reduction</t>
+          <t>onAttack</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>trueDamage</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
+        <v>0.12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="8">
@@ -745,41 +810,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>铁壁</t>
+          <t>等离子切割</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iron Wall</t>
+          <t>Plasma Cutter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>aura</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>受到伤害超过最大生命20%时，减伤10%持续1回合</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>damage_reduction_trigger</t>
-        </is>
-      </c>
+          <t>常驻光环：佩戴者攻击力提升8%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>buffAtk</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.08</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="9">
@@ -790,41 +858,48 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>弱点洞察</t>
+          <t>连锁反应</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Weakness Insight</t>
+          <t>Chain Reaction</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>aura</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>佩戴者暴击率+8%</t>
+          <t>击杀目标时触发：获得额外行动1次</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>crit_boost</t>
+          <t>onKill</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>extraAction</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="10">
@@ -835,41 +910,48 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>元素亲和</t>
+          <t>反物质裂解</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Elemental Affinity</t>
+          <t>Antimatter Fission</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>aura</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>佩戴者元素伤害+10%</t>
+          <t>攻击时触发：对目标造成攻击力18%的真实伤害</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>element_damage_boost</t>
+          <t>onAttack</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>trueDamage</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.18</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -880,41 +962,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>能量护盾</t>
+          <t>暗物质涌流</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Energy Shield</t>
+          <t>Dark Matter Surge</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>aura</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>受击时20%概率获得相当于10%最大生命值的护盾</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>shield_trigger</t>
-        </is>
-      </c>
+          <t>常驻光环：佩戴者攻击力提升15%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.1,0.2</t>
+          <t>buffAtk</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.15</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -925,41 +1010,48 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>坚韧体魄</t>
+          <t>量子隧穿</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tough Physique</t>
+          <t>Quantum Tunneling</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>aura</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>佩戴者最大生命值+8%，每回合恢复2%最大生命值</t>
+          <t>攻击时触发：无视防御造成攻击力25%的真实伤害</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>hp_regen</t>
+          <t>onAttack</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.08,0.02</t>
+          <t>trueDamage</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.25</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>220</v>
       </c>
     </row>
     <row r="13">
@@ -970,41 +1062,48 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>暴击精通</t>
+          <t>虚空坍缩</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Crit Mastery</t>
+          <t>Void Collapse</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>aura</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>佩戴者暴击率+10%，暴击伤害+20%</t>
+          <t>回合开始时触发：对敌方全体造成攻击力20%的真实伤害</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>crit_boost_crit_damage</t>
+          <t>onTurnStart</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.1,0.2</t>
+          <t>trueDamage</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="14">
@@ -1015,12 +1114,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>致命一击</t>
+          <t>超新星爆发</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fatal Strike</t>
+          <t>Supernova Burst</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1030,26 +1129,33 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>暴击时额外造成30%伤害</t>
+          <t>击杀目标时触发：对敌方全体造成攻击力30%的真实伤害</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>crit_extra_damage</t>
+          <t>onKill</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>trueDamage</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>280</v>
       </c>
     </row>
     <row r="15">
@@ -1060,12 +1166,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>战术分析</t>
+          <t>废铁壁垒</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tactical Analysis</t>
+          <t>Scrap Barricade</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1075,26 +1181,29 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>佩戴者攻击力+5%，闪避率+5%</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>atk_dodge_boost</t>
-        </is>
-      </c>
+          <t>常驻光环：佩戴者生命值提升3%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.05,0.05</t>
+          <t>buffHp</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.03</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -1105,12 +1214,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>弱点标记</t>
+          <t>辐射硬化</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Weakness Mark</t>
+          <t>Radiation Hardening</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1120,26 +1229,33 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>攻击时30%概率标记敌人，使其受到伤害增加10%持续2回合</t>
+          <t>受到伤害时触发：获得相当于最大生命值5%的护盾，持续2回合</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>mark_debuff</t>
+          <t>onDamageTaken</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.1,0.3</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="H16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>enemy_single</t>
-        </is>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="17">
@@ -1150,12 +1266,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>圣光庇护</t>
+          <t>合金镀层</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Holy Sanctuary</t>
+          <t>Alloy Coating</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1165,26 +1281,29 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>光属性角色生命值额外+10%，每回合恢复3%最大生命值</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>light_hp_regen</t>
-        </is>
-      </c>
+          <t>常驻光环：佩戴者减伤率提升5%</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.1,0.03</t>
+          <t>damageReduction</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.05</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="18">
@@ -1195,12 +1314,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>神圣护盾</t>
+          <t>纳米修复</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Divine Shield</t>
+          <t>Nano Repair</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1210,26 +1329,33 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>生命值首次低于30%时，获得相当于20%最大生命值的护盾（每场1次）</t>
+          <t>回合开始时触发：恢复最大生命值6%的生命</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>emergency_shield</t>
+          <t>onTurnStart</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>heal</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.06</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="19">
@@ -1240,12 +1366,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>光之祝福</t>
+          <t>碳纤维装甲</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Light's Blessing</t>
+          <t>Carbon Fiber Armor</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1255,26 +1381,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>全体友军减伤5%</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>team_damage_reduction</t>
-        </is>
-      </c>
+          <t>常驻光环：佩戴者生命值提升10%，减伤率提升8%</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>buffHp</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
+        <v>0.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="20">
@@ -1285,41 +1414,48 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>暗影侵蚀</t>
+          <t>自适应护盾</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Shadow Erosion</t>
+          <t>Adaptive Shield</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>aura</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>暗属性角色攻击力额外+10%，攻击附带5%最大生命值的暗影伤害</t>
+          <t>受到伤害时触发：获得相当于最大生命值10%的护盾，持续3回合</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>dark_atk_drain</t>
+          <t>onDamageTaken</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.1,0.05</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="21">
@@ -1330,41 +1466,44 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>暗影步</t>
+          <t>超导磁力场</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Shadow Step</t>
+          <t>Superconductor Field</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>aura</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>攻击后30%概率立即再行动一次（伤害减半）</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>extra_action</t>
-        </is>
-      </c>
+          <t>常驻光环：佩戴者减伤率提升12%，闪避率提升8%</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.3,0.5</t>
+          <t>damageReduction</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.12</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="22">
@@ -1375,12 +1514,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>灵魂收割</t>
+          <t>零点能量壁</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Soul Reaper</t>
+          <t>Zero-Point Barrier</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1390,26 +1529,33 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>击杀敌人后，攻击力永久提升5%（最高叠加3层）</t>
+          <t>受到伤害时触发：获得相当于最大生命值15%的护盾，持续3回合</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>kill_atk_stack</t>
+          <t>onDamageTaken</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.05,3</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.15</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>220</v>
       </c>
     </row>
     <row r="23">
@@ -1420,12 +1566,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>混沌共鸣</t>
+          <t>引力扭曲装甲</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chaos Resonance</t>
+          <t>Gravity Warp Armor</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1435,26 +1581,29 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>混合系角色全属性+8%</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>hybrid_all_boost</t>
-        </is>
-      </c>
+          <t>常驻光环：佩戴者生命值提升20%，减伤率提升15%</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>buffHp</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="24">
@@ -1465,12 +1614,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>混沌脉冲</t>
+          <t>维度折叠壁垒</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chaos Pulse</t>
+          <t>Dimensional Fold Barrier</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1480,26 +1629,33 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>每3回合释放混沌脉冲，对全体敌人造成佩戴者攻击力50%的伤害</t>
+          <t>生命值低于50%时触发：获得相当于最大生命值25%的护盾，持续4回合</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>periodic_aoe</t>
+          <t>onHpBelow</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.5,3</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>all_enemies</t>
-        </is>
+        <v>0.25</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>280</v>
       </c>
     </row>
     <row r="25">
@@ -1510,41 +1666,48 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>绝对防御</t>
+          <t>废料回收</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Absolute Defense</t>
+          <t>Scrap Recycler</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>aura</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>佩戴者减伤率+15%，免疫控制效果</t>
+          <t>回合开始时触发：恢复最大生命值3%的生命</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>damage_reduction_immune</t>
+          <t>onTurnStart</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>heal</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.03</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="26">
@@ -1555,12 +1718,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>堡垒结界</t>
+          <t>肾上腺素泵</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fortress Barrier</t>
+          <t>Adrenaline Pump</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1570,26 +1733,33 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>战斗开始时获得相当于30%最大生命值的护盾</t>
+          <t>战斗开始时触发：速度提升10%，持续3回合</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>battle_start_shield</t>
+          <t>onBattleStart</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>buffSpd</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="27">
@@ -1600,41 +1770,44 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>不屈意志</t>
+          <t>扫描模块</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Unyielding Will</t>
+          <t>Scan Module</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>modify</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>受到致命伤害时保留1点生命值（每场1次）</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>survive_lethal</t>
-        </is>
-      </c>
+          <t>永久提升佩戴者暴击率3%，闪避率3%</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>buffCrit</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.03</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>110</v>
       </c>
     </row>
     <row r="28">
@@ -1645,41 +1818,48 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>真实伤害</t>
+          <t>电磁加速</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>True Damage</t>
+          <t>EM Accelerator</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>aura</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>攻击附带目标最大生命值5%的真实伤害</t>
+          <t>战斗开始时触发：攻击力提升8%，速度提升8%，持续3回合</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>max_hp_true_damage</t>
+          <t>onBattleStart</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>buffAtk</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.08</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="29">
@@ -1690,12 +1870,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>末日之力</t>
+          <t>战术分析引擎</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Doom Power</t>
+          <t>Tactical Analysis Engine</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1705,26 +1885,29 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>佩戴者攻击力+15%，对生命值低于50%的敌人伤害额外+25%</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>atk_execute_boost</t>
-        </is>
-      </c>
+          <t>常驻光环：佩戴者速度提升10%，暴击率提升5%</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.15,0.25</t>
+          <t>buffSpd</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="30">
@@ -1735,12 +1918,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>毁灭连击</t>
+          <t>生物再生因子</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Destruction Combo</t>
+          <t>Bio Regen Factor</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1750,26 +1933,33 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>攻击后25%概率对同一目标追加一次80%伤害的攻击</t>
+          <t>回合开始时触发：恢复最大生命值8%的生命</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>follow_up_attack</t>
+          <t>onTurnStart</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.25,0.8</t>
+          <t>heal</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.08</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="31">
@@ -1780,41 +1970,48 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>万象更新</t>
+          <t>全息诱饵系统</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Universal Renewal</t>
+          <t>Holographic Decoy</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>aura</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>佩戴者全属性+10%</t>
+          <t>受到伤害时触发：闪避率提升15%，持续2回合</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>all_stat_boost</t>
+          <t>onDamageTaken</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>buffDodge</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.15</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="32">
@@ -1825,12 +2022,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>随机强化</t>
+          <t>时空锚点</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Random Boost</t>
+          <t>Spacetime Anchor</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1840,26 +2037,33 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>每回合开始时随机获得一种增益：攻击+15%/防御+15%/速度+15%</t>
+          <t>战斗开始时触发：全体友方攻击力提升10%，速度提升10%，持续3回合</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>random_buff</t>
+          <t>onBattleStart</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>buffAtk</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>0.1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>220</v>
       </c>
     </row>
     <row r="33">
@@ -1870,41 +2074,44 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>万象归元</t>
+          <t>熵减力场</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Universal Unity</t>
+          <t>Entropy Reduction Field</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>aura</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>每5回合释放万象归元，全体友军恢复15%最大生命值并提升10%全属性持续2回合</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>periodic_team_buff</t>
-        </is>
-      </c>
+          <t>常驻光环：佩戴者速度提升15%，暴击率提升10%，闪避率提升10%</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.15,0.1,2,5</t>
+          <t>buffSpd</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
+        <v>0.15</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="34">
@@ -1915,41 +2122,48 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>创世守护</t>
+          <t>因果律干扰器</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Genesis Guard</t>
+          <t>Causality Interferometer</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>aura</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>佩戴者生命值+20%，减伤率+10%，每回合恢复5%最大生命值</t>
+          <t>生命值低于30%时触发：获得额外行动1次，攻击力提升20%，持续2回合</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>legendary_defense</t>
+          <t>onHpBelow</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.2,0.1,0.05</t>
+          <t>extraAction</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>6</v>
+      </c>
+      <c r="L34" t="n">
+        <v>280</v>
       </c>
     </row>
     <row r="35">
@@ -1960,12 +2174,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>神之庇佑</t>
+          <t>奇点引擎</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>God's Protection</t>
+          <t>Singularity Engine</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1975,476 +2189,33 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>战斗开始时全体友军获得15%最大生命值的护盾</t>
+          <t>回合开始时触发：恢复最大生命值12%，攻击力提升10%，持续2回合</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>team_start_shield</t>
+          <t>onTurnStart</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>heal</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>CSK033</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>不朽之身</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Immortal Body</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>trigger</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>首次受到致命伤害时以50%生命值复活（每场1次）</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>revive</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>CSK034</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>生命之泉</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Fountain of Life</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>aura</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>全体友军每回合恢复5%最大生命值</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>team_regen</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>CSK035</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>湮灭之力</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Annihilation Power</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>aura</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>佩戴者攻击力+25%，暴击伤害+40%</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>legendary_attack</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>0.25,0.4</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>CSK036</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>连续打击</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Chain Strike</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>trigger</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>击杀敌人后立即对随机敌人造成120%伤害的追击（每回合最多1次）</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>kill_chain</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>enemy_single</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>CSK037</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>破甲</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Armor Break</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>aura</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>攻击无视目标30%防御力</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>armor_penetration</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>CSK038</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>死亡标记</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Death Mark</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>trigger</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>攻击时20%概率标记敌人，标记目标3回合后受到佩戴者攻击力200%的真实伤害</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>death_mark</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>0.2,3,2.0</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>3</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>enemy_single</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>CSK039</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>世界树祝福</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>World Tree Blessing</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>aura</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>佩戴者全属性+15%，全体友军每回合恢复3%最大生命值</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>legendary_all_team_regen</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>0.15,0.03</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>CSK040</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>自然之力</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Force of Nature</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>trigger</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>每回合开始时，随机为一名友军提供攻击+20%或防御+20%的增益持续2回合</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>random_team_buff</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>0.2,2</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I35" t="n">
         <v>2</v>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>team_single</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>CSK041</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>生命绽放</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Life Bloom</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>trigger</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>友军生命值低于40%时自动触发，恢复其25%最大生命值（每回合1次）</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>auto_heal</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>team_single</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>CSK042</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>创世之息</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Breath of Genesis</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>trigger</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>每5回合释放创世之息，全体友军恢复30%最大生命值并清除所有负面效果</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>periodic_heal_cleanse</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>0.3,5</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>260</v>
       </c>
     </row>
   </sheetData>
